--- a/manual-testing/test-scenarios.xlsx
+++ b/manual-testing/test-scenarios.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="94">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>Sosyal medya ikonları kullanıcıyı ilgili sosyal medya sayfalarına yönlendirmelidir.</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
 </sst>
 </file>
@@ -575,11 +581,11 @@
   <dxfs count="6">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -595,11 +601,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -964,7 +970,7 @@
         <v>60</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1010,7 +1016,7 @@
         <v>62</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1033,7 +1039,7 @@
         <v>63</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1194,7 +1200,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1309,7 +1315,7 @@
         <v>75</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1332,7 +1338,7 @@
         <v>76</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1424,7 +1430,7 @@
         <v>88</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1447,7 +1453,7 @@
         <v>89</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1470,7 +1476,7 @@
         <v>90</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1493,7 +1499,7 @@
         <v>91</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1509,23 +1515,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D25">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",D2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",D2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",D2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D25">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E25">
       <formula1>"Functional,Negative,UI/UX,Exploratory,Smoke"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G25">
+      <formula1>"Not Executed,In Progress,Passed,Failed,Blocked,Skipped,"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
